--- a/samples/reports/invoice/template.xlsx
+++ b/samples/reports/invoice/template.xlsx
@@ -5,7 +5,7 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$34</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="R3d91fb1fb49543ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="R672ca50bdcfe473e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/samples/reports/invoice/template.xlsx
+++ b/samples/reports/invoice/template.xlsx
@@ -5,7 +5,7 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$34</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="R672ca50bdcfe473e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="Rcddb212b468b4f2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -235,6 +235,9 @@
       <x:c r="C8" s="9">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="D8" s="9"/>
+      <x:c r="E8" s="9"/>
+      <x:c r="F8" s="9"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="4" t="inlineStr">

--- a/samples/reports/invoice/template.xlsx
+++ b/samples/reports/invoice/template.xlsx
@@ -5,7 +5,7 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$34</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="Rcddb212b468b4f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="Ra50ad83591e243c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -161,6 +161,42 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="254000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rbcb4d422e2994f14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="762000" cy="254000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
@@ -487,5 +523,6 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4f2aeeabcf84019"/>
 </x:worksheet>
 </file>
--- a/samples/reports/invoice/template.xlsx
+++ b/samples/reports/invoice/template.xlsx
@@ -5,7 +5,7 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$34</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="Ra50ad83591e243c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="Rd17161ca7e6e4681"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,7 +177,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rbcb4d422e2994f14"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc2dfe72d1dba4022"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -192,6 +192,120 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>-76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="889000" cy="279400"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Shape3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-720000">
+          <a:off x="0" y="0"/>
+          <a:ext cx="889000" cy="279400"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchor="ctr"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr sz="1000"/>
+            <a:t>見本</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="508000" cy="177800"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Shape4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="508000" cy="177800"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="2E8B57"/>
+        </a:solidFill>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1397000" cy="304800"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Shape5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="1397000" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="wedgeRoundRectCallout">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchor="ctr"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr sz="1000"/>
+            <a:t>ご確認ください</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
@@ -523,6 +637,6 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4f2aeeabcf84019"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eb7e9e0c5024bf3"/>
 </x:worksheet>
 </file>
--- a/samples/reports/invoice/template.xlsx
+++ b/samples/reports/invoice/template.xlsx
@@ -5,7 +5,7 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$34</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="Rd17161ca7e6e4681"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="R57f02ce9ad9c4402"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,7 +177,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc2dfe72d1dba4022"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd76edcd2a2104fa7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -308,6 +308,184 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="533400" cy="355600"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Shape6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="533400" cy="355600"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="star6">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="FFF3B0"/>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:srgbClr val="FFC300"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="C77800"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="2700000"/>
+        </a:gradFill>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="355600"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Shape7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="762000" cy="355600"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="flowChartTerminator">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="E0F7FA"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="0288D1"/>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect/>
+          </a:path>
+        </a:gradFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="01579B"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1651000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="584200" cy="304800"/>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Connector8"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="584200" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="444444"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2413000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="825500" cy="431800"/>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="9" name="Group9"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-480000">
+          <a:off x="0" y="0"/>
+          <a:ext cx="825500" cy="431800"/>
+          <a:chOff x="0" y="0"/>
+          <a:chExt cx="825500" cy="431800"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="10" name="GroupChild10"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:off x="0" y="0"/>
+            <a:ext cx="825500" cy="431800"/>
+          </a:xfrm>
+          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:sp>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="11" name="GroupChild11"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:off x="152400" y="114300"/>
+            <a:ext cx="520700" cy="203200"/>
+          </a:xfrm>
+          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -376,6 +554,7 @@
         <x:v>46142</x:v>
       </x:c>
     </x:row>
+    <x:row r="6" ht="34" customHeight="1"/>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="12" t="inlineStr">
         <x:is>
@@ -637,6 +816,6 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eb7e9e0c5024bf3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a2361a0c349497b"/>
 </x:worksheet>
 </file>
--- a/samples/reports/invoice/template.xlsx
+++ b/samples/reports/invoice/template.xlsx
@@ -5,7 +5,7 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$34</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="R57f02ce9ad9c4402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="R51f6f6cb32fb4ab0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,7 +177,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd76edcd2a2104fa7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R02544466fe1143db"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -393,6 +393,72 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>3429000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="381000"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Shape8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="762000" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="flowChartInputOutput">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="444444"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>4572000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="381000"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Shape9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="762000" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="flowChartInputOutput">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="444444"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>1651000</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
@@ -400,7 +466,7 @@
     <xdr:ext cx="584200" cy="304800"/>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="Connector8"/>
+        <xdr:cNvPr id="10" name="Connector10"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -423,6 +489,39 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>4191000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="381000" cy="381000"/>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Connector11"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="8" idx="3"/>
+          <a:endCxn xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="9" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="381000" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="444444"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>2413000</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -430,7 +529,7 @@
     <xdr:ext cx="825500" cy="431800"/>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="9" name="Group9"/>
+        <xdr:cNvPr id="12" name="Group12"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
@@ -443,7 +542,7 @@
       </xdr:grpSpPr>
       <xdr:sp>
         <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="GroupChild10"/>
+          <xdr:cNvPr id="13" name="GroupChild13"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -464,7 +563,7 @@
       </xdr:sp>
       <xdr:sp>
         <xdr:nvSpPr>
-          <xdr:cNvPr id="11" name="GroupChild11"/>
+          <xdr:cNvPr id="14" name="GroupChild14"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -816,6 +915,6 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a2361a0c349497b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref2ad2776cea4c19"/>
 </x:worksheet>
 </file>
--- a/samples/reports/invoice/template.xlsx
+++ b/samples/reports/invoice/template.xlsx
@@ -5,7 +5,7 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$34</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="Rd17161ca7e6e4681"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="R51f6f6cb32fb4ab0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,7 +177,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc2dfe72d1dba4022"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R02544466fe1143db"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -308,6 +308,283 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="533400" cy="355600"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Shape6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="533400" cy="355600"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="star6">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="FFF3B0"/>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:srgbClr val="FFC300"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="C77800"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="2700000"/>
+        </a:gradFill>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="355600"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Shape7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="762000" cy="355600"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="flowChartTerminator">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="E0F7FA"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="0288D1"/>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect/>
+          </a:path>
+        </a:gradFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="01579B"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>3429000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="381000"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Shape8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="762000" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="flowChartInputOutput">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="444444"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>4572000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="381000"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Shape9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="762000" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="flowChartInputOutput">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="444444"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1651000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="584200" cy="304800"/>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Connector10"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="584200" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="444444"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>4191000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="381000" cy="381000"/>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Connector11"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="8" idx="3"/>
+          <a:endCxn xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="9" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="381000" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="444444"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2413000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="825500" cy="431800"/>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="12" name="Group12"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-480000">
+          <a:off x="0" y="0"/>
+          <a:ext cx="825500" cy="431800"/>
+          <a:chOff x="0" y="0"/>
+          <a:chExt cx="825500" cy="431800"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="13" name="GroupChild13"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:off x="0" y="0"/>
+            <a:ext cx="825500" cy="431800"/>
+          </a:xfrm>
+          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:sp>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="GroupChild14"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:off x="152400" y="114300"/>
+            <a:ext cx="520700" cy="203200"/>
+          </a:xfrm>
+          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -376,6 +653,7 @@
         <x:v>46142</x:v>
       </x:c>
     </x:row>
+    <x:row r="6" ht="34" customHeight="1"/>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="12" t="inlineStr">
         <x:is>
@@ -637,6 +915,6 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eb7e9e0c5024bf3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref2ad2776cea4c19"/>
 </x:worksheet>
 </file>
--- a/samples/reports/invoice/template.xlsx
+++ b/samples/reports/invoice/template.xlsx
@@ -5,7 +5,7 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$34</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="R51f6f6cb32fb4ab0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="Rd648f332e5544bf6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,15 +177,46 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R02544466fe1143db"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb92692f702c44105"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
           <a:off x="0" y="0"/>
           <a:ext cx="762000" cy="254000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5588000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="381000" cy="381000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5e5d9d6963e24768"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="1200000">
+          <a:off x="0" y="0"/>
+          <a:ext cx="381000" cy="381000"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -204,7 +235,7 @@
     <xdr:ext cx="889000" cy="279400"/>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Shape3"/>
+        <xdr:cNvPr id="4" name="Shape4"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -246,7 +277,7 @@
     <xdr:ext cx="508000" cy="177800"/>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Shape4"/>
+        <xdr:cNvPr id="5" name="Shape5"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -274,7 +305,7 @@
     <xdr:ext cx="1397000" cy="304800"/>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Shape5"/>
+        <xdr:cNvPr id="6" name="Shape6"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -318,7 +349,7 @@
     <xdr:ext cx="533400" cy="355600"/>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Shape6"/>
+        <xdr:cNvPr id="7" name="Shape7"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -357,7 +388,7 @@
     <xdr:ext cx="762000" cy="355600"/>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Shape7"/>
+        <xdr:cNvPr id="8" name="Shape8"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -400,7 +431,7 @@
     <xdr:ext cx="762000" cy="381000"/>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Shape8"/>
+        <xdr:cNvPr id="9" name="Shape9"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -433,7 +464,7 @@
     <xdr:ext cx="762000" cy="381000"/>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Shape9"/>
+        <xdr:cNvPr id="10" name="Shape10"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -466,7 +497,7 @@
     <xdr:ext cx="584200" cy="304800"/>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="Connector10"/>
+        <xdr:cNvPr id="11" name="Connector11"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -496,10 +527,10 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Connector11"/>
+        <xdr:cNvPr id="12" name="Connector12"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="8" idx="3"/>
-          <a:endCxn xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="9" idx="1"/>
+          <a:stCxn xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="9" idx="3"/>
+          <a:endCxn xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -529,7 +560,7 @@
     <xdr:ext cx="825500" cy="431800"/>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="12" name="Group12"/>
+        <xdr:cNvPr id="13" name="Group13"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
@@ -542,7 +573,7 @@
       </xdr:grpSpPr>
       <xdr:sp>
         <xdr:nvSpPr>
-          <xdr:cNvPr id="13" name="GroupChild13"/>
+          <xdr:cNvPr id="14" name="GroupChild14"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -563,7 +594,7 @@
       </xdr:sp>
       <xdr:sp>
         <xdr:nvSpPr>
-          <xdr:cNvPr id="14" name="GroupChild14"/>
+          <xdr:cNvPr id="15" name="GroupChild15"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -915,6 +946,6 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref2ad2776cea4c19"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb61fb10aaf44bd0"/>
 </x:worksheet>
 </file>
--- a/samples/reports/invoice/template.xlsx
+++ b/samples/reports/invoice/template.xlsx
@@ -5,7 +5,7 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$F$34</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="Rd648f332e5544bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書" sheetId="1" r:id="Raf797723c4ec40a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,7 +177,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb92692f702c44105"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6e01ed06eb694865"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -208,7 +208,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5e5d9d6963e24768"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rfa9649077d944df6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -490,6 +490,138 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1016000" cy="228600"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Shape11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="1016000" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="borderCallout2">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+            <a:gd name="adj2" fmla="val 100000"/>
+            <a:gd name="adj3" fmla="val 50000"/>
+            <a:gd name="adj4" fmla="val 125000"/>
+            <a:gd name="adj5" fmla="val 150000"/>
+            <a:gd name="adj6" fmla="val 160000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchor="ctr"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr sz="1000"/>
+            <a:t>要確認</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2032000</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="355600" cy="355600"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Shape12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="355600" cy="355600"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchor="ctr"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr sz="1000"/>
+            <a:t>済</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2425700</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>330200</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="215900" cy="152400"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Shape13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" flipH="1">
+          <a:off x="0" y="0"/>
+          <a:ext cx="215900" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="2E8B57"/>
+        </a:solidFill>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>1651000</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
@@ -497,7 +629,7 @@
     <xdr:ext cx="584200" cy="304800"/>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Connector11"/>
+        <xdr:cNvPr id="14" name="Connector14"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -527,7 +659,7 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="Connector12"/>
+        <xdr:cNvPr id="15" name="Connector15"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="9" idx="3"/>
           <a:endCxn xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10" idx="1"/>
@@ -560,7 +692,7 @@
     <xdr:ext cx="825500" cy="431800"/>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="13" name="Group13"/>
+        <xdr:cNvPr id="16" name="Group16"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
@@ -573,7 +705,7 @@
       </xdr:grpSpPr>
       <xdr:sp>
         <xdr:nvSpPr>
-          <xdr:cNvPr id="14" name="GroupChild14"/>
+          <xdr:cNvPr id="17" name="GroupChild17"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -594,7 +726,7 @@
       </xdr:sp>
       <xdr:sp>
         <xdr:nvSpPr>
-          <xdr:cNvPr id="15" name="GroupChild15"/>
+          <xdr:cNvPr id="18" name="GroupChild18"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -946,6 +1078,6 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb61fb10aaf44bd0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R110103cb0be544b8"/>
 </x:worksheet>
 </file>